--- a/롯데마트/롯데마트 마스터 정보.xlsx
+++ b/롯데마트/롯데마트 마스터 정보.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>바코드</t>
   </si>
@@ -41,9 +41,6 @@
     <t>접착식원터치도어스토퍼(소)</t>
   </si>
   <si>
-    <t>접착식원터치도어스토퍼(대)</t>
-  </si>
-  <si>
     <t>솔루엠25W초고속충전기(C타입)</t>
   </si>
   <si>
@@ -138,9 +135,6 @@
   </si>
   <si>
     <t>툴스피아미니글루건</t>
-  </si>
-  <si>
-    <t>핫멜트스틱(소)10p</t>
   </si>
   <si>
     <t>에이원접착제브러쉬형7g</t>
@@ -202,6 +196,15 @@
   </si>
   <si>
     <t>몬스툴정밀용드라이버세트</t>
+  </si>
+  <si>
+    <t>툴스피아고속맥세이프보조배터리</t>
+  </si>
+  <si>
+    <t>툴스피아메탈고속맥세이프보조배터리</t>
+  </si>
+  <si>
+    <t>툴스피아자석맥세이프핸드폰거치대</t>
   </si>
 </sst>
 </file>
@@ -321,7 +324,87 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -608,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18.625" style="5" customWidth="1"/>
@@ -640,10 +723,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
-        <v>8809148120623</v>
+        <v>8809580801524</v>
       </c>
       <c r="B3" s="5">
-        <v>202304240002</v>
+        <v>2023051800001</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>4</v>
@@ -651,10 +734,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
-        <v>8809580801524</v>
+        <v>8809599841009</v>
       </c>
       <c r="B4" s="5">
-        <v>2023051800001</v>
+        <v>2023071100001</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -662,10 +745,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>8809599841009</v>
+        <v>8809599840996</v>
       </c>
       <c r="B5" s="5">
-        <v>2023071100001</v>
+        <v>2023071100002</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>6</v>
@@ -673,10 +756,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
-        <v>8809599840996</v>
+        <v>8809599841016</v>
       </c>
       <c r="B6" s="5">
-        <v>2023071100002</v>
+        <v>2023071100003</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
@@ -684,10 +767,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
-        <v>8809599841016</v>
+        <v>8809580801678</v>
       </c>
       <c r="B7" s="5">
-        <v>2023071100003</v>
+        <v>2023071700001</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>8</v>
@@ -695,10 +778,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
-        <v>8809580801678</v>
+        <v>8809580801579</v>
       </c>
       <c r="B8" s="5">
-        <v>2023071700001</v>
+        <v>2023071700002</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>9</v>
@@ -706,10 +789,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
-        <v>8809580801579</v>
+        <v>8809774029697</v>
       </c>
       <c r="B9" s="5">
-        <v>2023071700002</v>
+        <v>2023101100001</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>10</v>
@@ -717,10 +800,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
-        <v>8809774029697</v>
+        <v>8809774029116</v>
       </c>
       <c r="B10" s="5">
-        <v>2023101100001</v>
+        <v>2023101100002</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
@@ -728,10 +811,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
-        <v>8809774029116</v>
+        <v>8809774028102</v>
       </c>
       <c r="B11" s="5">
-        <v>2023101100002</v>
+        <v>2023101100005</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>12</v>
@@ -739,10 +822,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
-        <v>8809774028102</v>
+        <v>8809774023930</v>
       </c>
       <c r="B12" s="5">
-        <v>2023101100005</v>
+        <v>2023101100008</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>13</v>
@@ -750,10 +833,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
-        <v>8809774023930</v>
+        <v>8809774023954</v>
       </c>
       <c r="B13" s="5">
-        <v>2023101100008</v>
+        <v>2023112400002</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>14</v>
@@ -761,10 +844,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
-        <v>8809774023954</v>
+        <v>8809774028119</v>
       </c>
       <c r="B14" s="5">
-        <v>2023112400002</v>
+        <v>2023120800001</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>15</v>
@@ -772,10 +855,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
-        <v>8809774028119</v>
+        <v>8809148129442</v>
       </c>
       <c r="B15" s="5">
-        <v>2023120800001</v>
+        <v>2024051600001</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>16</v>
@@ -783,10 +866,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
-        <v>8809148129442</v>
+        <v>8809599840507</v>
       </c>
       <c r="B16" s="5">
-        <v>2024051600001</v>
+        <v>2024061000001</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>17</v>
@@ -794,10 +877,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
-        <v>8809599840507</v>
+        <v>8809599840002</v>
       </c>
       <c r="B17" s="5">
-        <v>2024061000001</v>
+        <v>2024061000012</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>18</v>
@@ -805,10 +888,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
-        <v>8809599840002</v>
+        <v>8809599840019</v>
       </c>
       <c r="B18" s="5">
-        <v>2024061000012</v>
+        <v>2024061000013</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>19</v>
@@ -816,10 +899,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
-        <v>8809599840019</v>
+        <v>8809599840026</v>
       </c>
       <c r="B19" s="5">
-        <v>2024061000013</v>
+        <v>2024061000014</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>20</v>
@@ -827,10 +910,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
-        <v>8809599840026</v>
+        <v>8809599840118</v>
       </c>
       <c r="B20" s="5">
-        <v>2024061000014</v>
+        <v>2024061000015</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>21</v>
@@ -838,10 +921,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
-        <v>8809599840118</v>
+        <v>8809599840125</v>
       </c>
       <c r="B21" s="5">
-        <v>2024061000015</v>
+        <v>2024061000016</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>22</v>
@@ -849,10 +932,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
-        <v>8809599840125</v>
+        <v>8809599840132</v>
       </c>
       <c r="B22" s="5">
-        <v>2024061000016</v>
+        <v>2024061000017</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>23</v>
@@ -860,10 +943,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
-        <v>8809599840132</v>
+        <v>8809599840149</v>
       </c>
       <c r="B23" s="5">
-        <v>2024061000017</v>
+        <v>2024061000018</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>24</v>
@@ -871,10 +954,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
-        <v>8809599840149</v>
+        <v>8809599841443</v>
       </c>
       <c r="B24" s="5">
-        <v>2024061000018</v>
+        <v>2024102100002</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>25</v>
@@ -882,10 +965,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
-        <v>8809599841443</v>
+        <v>8809148128704</v>
       </c>
       <c r="B25" s="5">
-        <v>2024102100002</v>
+        <v>2024112000001</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>26</v>
@@ -893,10 +976,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
-        <v>8809148128704</v>
+        <v>8809148128698</v>
       </c>
       <c r="B26" s="5">
-        <v>2024112000001</v>
+        <v>2024112000002</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>27</v>
@@ -904,10 +987,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
-        <v>8809148128698</v>
+        <v>8809148128681</v>
       </c>
       <c r="B27" s="5">
-        <v>2024112000002</v>
+        <v>2024112000003</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>28</v>
@@ -915,10 +998,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
-        <v>8809148128681</v>
+        <v>8809148128674</v>
       </c>
       <c r="B28" s="5">
-        <v>2024112000003</v>
+        <v>2024112000004</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>29</v>
@@ -926,10 +1009,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
-        <v>8809148128674</v>
+        <v>8809695510687</v>
       </c>
       <c r="B29" s="5">
-        <v>2024112000004</v>
+        <v>2024121300001</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>30</v>
@@ -937,10 +1020,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
-        <v>8809695510687</v>
+        <v>8809198502578</v>
       </c>
       <c r="B30" s="5">
-        <v>2024121300001</v>
+        <v>2025020600001</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>31</v>
@@ -948,10 +1031,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
-        <v>8809198502578</v>
+        <v>8809198502585</v>
       </c>
       <c r="B31" s="5">
-        <v>2025020600001</v>
+        <v>2025020600002</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>32</v>
@@ -959,10 +1042,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
-        <v>8809198502585</v>
+        <v>8809148128773</v>
       </c>
       <c r="B32" s="5">
-        <v>2025020600002</v>
+        <v>2025030500001</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>33</v>
@@ -970,10 +1053,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
-        <v>8809148128773</v>
+        <v>8809148128797</v>
       </c>
       <c r="B33" s="5">
-        <v>2025030500001</v>
+        <v>2025030500002</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>34</v>
@@ -981,10 +1064,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
-        <v>8809148128797</v>
+        <v>8809057403862</v>
       </c>
       <c r="B34" s="5">
-        <v>2025030500002</v>
+        <v>8809057403862</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>35</v>
@@ -992,10 +1075,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
-        <v>8809057403862</v>
+        <v>8809550590236</v>
       </c>
       <c r="B35" s="5">
-        <v>8809057403862</v>
+        <v>8809550590090</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>36</v>
@@ -1003,10 +1086,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
-        <v>8809057634778</v>
+        <v>8809550590113</v>
       </c>
       <c r="B36" s="5">
-        <v>8809057634778</v>
+        <v>8809550590113</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>37</v>
@@ -1014,10 +1097,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
-        <v>8809550590236</v>
+        <v>8809550590205</v>
       </c>
       <c r="B37" s="5">
-        <v>8809550590090</v>
+        <v>8809550590205</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>38</v>
@@ -1025,10 +1108,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
-        <v>8809550590113</v>
+        <v>8809599841023</v>
       </c>
       <c r="B38" s="5">
-        <v>8809550590113</v>
+        <v>8809599841023</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>39</v>
@@ -1036,10 +1119,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
-        <v>8809550590205</v>
+        <v>8809599841030</v>
       </c>
       <c r="B39" s="5">
-        <v>8809550590205</v>
+        <v>8809599841030</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>40</v>
@@ -1047,10 +1130,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
-        <v>8809599841023</v>
+        <v>8809599841047</v>
       </c>
       <c r="B40" s="5">
-        <v>8809599841023</v>
+        <v>8809599841047</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>41</v>
@@ -1058,10 +1141,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
-        <v>8809599841030</v>
+        <v>8809599841078</v>
       </c>
       <c r="B41" s="5">
-        <v>8809599841030</v>
+        <v>8809599841078</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>42</v>
@@ -1069,10 +1152,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
-        <v>8809599841047</v>
+        <v>8809599841085</v>
       </c>
       <c r="B42" s="5">
-        <v>8809599841047</v>
+        <v>8809599841085</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>43</v>
@@ -1080,10 +1163,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
-        <v>8809599841078</v>
+        <v>8809599841108</v>
       </c>
       <c r="B43" s="5">
-        <v>8809599841078</v>
+        <v>8809599841108</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>44</v>
@@ -1091,10 +1174,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
-        <v>8809599841085</v>
+        <v>8809599841115</v>
       </c>
       <c r="B44" s="5">
-        <v>8809599841085</v>
+        <v>8809599841115</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>45</v>
@@ -1102,10 +1185,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
-        <v>8809599841108</v>
+        <v>8809599841122</v>
       </c>
       <c r="B45" s="5">
-        <v>8809599841108</v>
+        <v>8809599841122</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>46</v>
@@ -1113,10 +1196,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
-        <v>8809599841115</v>
+        <v>8809599841139</v>
       </c>
       <c r="B46" s="5">
-        <v>8809599841115</v>
+        <v>8809599841139</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>47</v>
@@ -1124,10 +1207,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
-        <v>8809599841122</v>
+        <v>8809599841160</v>
       </c>
       <c r="B47" s="5">
-        <v>8809599841122</v>
+        <v>8809599841160</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>48</v>
@@ -1135,10 +1218,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
-        <v>8809599841139</v>
+        <v>8809599841177</v>
       </c>
       <c r="B48" s="5">
-        <v>8809599841139</v>
+        <v>8809599841177</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>49</v>
@@ -1146,88 +1229,110 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
-        <v>8809599841160</v>
+        <v>8809599841184</v>
       </c>
       <c r="B49" s="5">
-        <v>8809599841160</v>
+        <v>8809599841184</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="5">
-        <v>8809599841177</v>
-      </c>
-      <c r="B50" s="5">
-        <v>8809599841177</v>
-      </c>
-      <c r="C50" s="4" t="s">
+    <row r="50" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="6">
+        <v>8809057630046</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="5">
-        <v>8809599841184</v>
-      </c>
-      <c r="B51" s="5">
-        <v>8809599841184</v>
-      </c>
-      <c r="C51" s="4" t="s">
+      <c r="C50" s="7" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="6">
+        <v>8809057634778</v>
+      </c>
+      <c r="B51" s="6">
+        <v>8809057634778</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
-        <v>8809057630046</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>53</v>
+        <v>8809148120623</v>
+      </c>
+      <c r="B52" s="6">
+        <v>202304240002</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6">
-        <v>8809057634778</v>
-      </c>
-      <c r="B53" s="6">
-        <v>8809057634778</v>
-      </c>
-      <c r="C53" s="7" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="5">
+        <v>8809057401011</v>
+      </c>
+      <c r="B53" s="5">
+        <v>2025091900001</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="54" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6">
-        <v>8809148120623</v>
-      </c>
-      <c r="B54" s="6">
-        <v>202304240002</v>
-      </c>
-      <c r="C54" s="7" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
+        <v>8800272200083</v>
+      </c>
+      <c r="B54" s="5">
+        <v>2026060600001</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
-        <v>8809057401011</v>
+        <v>8800272201301</v>
       </c>
       <c r="B55" s="5">
-        <v>2025091900001</v>
+        <v>2026060600002</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="5">
+        <v>8800272205002</v>
+      </c>
+      <c r="B56" s="5">
+        <v>2026060600004</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 A53:A1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="A1 A51:A53 A57:A1048576">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>8809057630046</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54:A56">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>8809057630046</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/롯데마트/롯데마트 마스터 정보.xlsx
+++ b/롯데마트/롯데마트 마스터 정보.xlsx
@@ -324,57 +324,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
